--- a/docs/tables/capture_comparison_summary.xlsx
+++ b/docs/tables/capture_comparison_summary.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="per_reconstruction" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="capture_sensitivity" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="capture_comparison" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +17,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
@@ -39,11 +42,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
+        <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -51,14 +54,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <top style="medium">
+        <color rgb="009AA07A"/>
+      </top>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,31 +436,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>object</t>
@@ -456,7 +472,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>approach</t>
+          <t>capture approach</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -471,147 +487,179 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>accuracy@3cm (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>completeness@3cm (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>F1@3cm (%)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>F1 95% CI lo</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>F1 95% CI hi</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Accuracy@3cm (%)</t>
+          <t>accuracy@5cm (%)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Completeness@3cm (%)</t>
+          <t>completeness@5cm (%)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>F1@5cm (%)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy@10cm (%)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>completeness@10cm (%)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>F1@10cm (%)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ΔF1@10-3cm (pp)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>F1@3cm 95% CI lo</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>F1@3cm 95% CI hi</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>accuracy median (cm)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>completeness median (cm)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>inlier RMSE@3cm (cm)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>reg-rate (%)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>points raw</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>points density-matched</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>excluded as gap</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>DBSCAN (ft/eps/mp)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>excluded pts</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>blocks acc</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>blocks comp</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>bollard_003</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>T1 close-ups+orbit</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>T1 · close-range + distant</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>COLMAP</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>exp_087</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>80.17</v>
-      </c>
-      <c r="F2" t="n">
-        <v>76.47</v>
-      </c>
-      <c r="G2" t="n">
-        <v>83.81</v>
-      </c>
-      <c r="H2" t="n">
-        <v>89.29000000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>72.75</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.689</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="M2" t="n">
-        <v>100</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="E2" s="2" t="n">
+        <v>88.88</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>70.39</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>78.56</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>99.06</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>91.13</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>94.93000000000001</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>99.73999999999999</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>74.89</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>81.97</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1.854</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="T2" s="2" t="n">
         <v>105933</v>
       </c>
-      <c r="O2" t="n">
+      <c r="U2" s="2" t="n">
         <v>3847</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="V2" s="2" t="n">
+        <v>754</v>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>1110</v>
-      </c>
-      <c r="R2" t="n">
-        <v>237</v>
-      </c>
-      <c r="S2" t="n">
-        <v>258</v>
       </c>
     </row>
     <row r="3">
@@ -622,7 +670,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>T2 overhead only</t>
+          <t>T2 · close-range only</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -635,52 +683,64 @@
           <t>exp_088</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>84.56</v>
+      <c r="E3" t="n">
+        <v>92.38</v>
       </c>
       <c r="F3" t="n">
-        <v>81.23</v>
+        <v>73.83</v>
       </c>
       <c r="G3" t="n">
-        <v>87.34999999999999</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>91.84</v>
+        <v>98.87</v>
       </c>
       <c r="I3" t="n">
-        <v>78.34999999999999</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8159999999999999</v>
+        <v>96.47</v>
       </c>
       <c r="K3" t="n">
-        <v>1.467</v>
+        <v>99.78</v>
       </c>
       <c r="L3" t="n">
-        <v>1.02</v>
+        <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>100</v>
+        <v>99.89</v>
       </c>
       <c r="N3" t="n">
+        <v>17.82</v>
+      </c>
+      <c r="O3" t="n">
+        <v>78.84</v>
+      </c>
+      <c r="P3" t="n">
+        <v>84.95999999999999</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.688</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="T3" t="n">
         <v>36609</v>
       </c>
-      <c r="O3" t="n">
-        <v>2716</v>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>2715</v>
+      </c>
+      <c r="V3" t="n">
+        <v>419</v>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>644</v>
-      </c>
-      <c r="R3" t="n">
-        <v>206</v>
-      </c>
-      <c r="S3" t="n">
-        <v>258</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +751,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T3 full orbit only</t>
+          <t>T3 · distant only</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -705,120 +765,144 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>84.04000000000001</v>
+        <v>88.25</v>
       </c>
       <c r="F4" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="G4" t="n">
-        <v>86.81999999999999</v>
+        <v>78.15000000000001</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>82.89</v>
       </c>
       <c r="H4" t="n">
-        <v>86.59</v>
+        <v>99.37</v>
       </c>
       <c r="I4" t="n">
-        <v>81.64</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.146</v>
+        <v>98.14</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>98.75</v>
       </c>
       <c r="K4" t="n">
-        <v>1.45</v>
+        <v>99.95</v>
       </c>
       <c r="L4" t="n">
-        <v>1.387</v>
-      </c>
-      <c r="M4" t="n">
-        <v>100</v>
+        <v>100</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>99.98</v>
       </c>
       <c r="N4" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="O4" t="n">
+        <v>79.97</v>
+      </c>
+      <c r="P4" t="n">
+        <v>85.47</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.227</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="T4" t="n">
         <v>167287</v>
       </c>
-      <c r="O4" t="n">
+      <c r="U4" t="n">
         <v>5592</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="V4" t="n">
+        <v>1295</v>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>1730</v>
-      </c>
-      <c r="R4" t="n">
-        <v>296</v>
-      </c>
-      <c r="S4" t="n">
-        <v>258</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>bollard_003</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>T1 close-ups+orbit</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>T1 · close-range + distant</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>MASt3R-GA</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>exp_090</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>93.79000000000001</v>
-      </c>
-      <c r="F5" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>95.09999999999999</v>
-      </c>
-      <c r="H5" t="n">
-        <v>88.31</v>
-      </c>
-      <c r="I5" t="n">
-        <v>100</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.034</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.502</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M5" t="n">
-        <v>100</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="E5" s="2" t="n">
+        <v>88.88</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>97.66</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>93.06999999999999</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>94.36</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>1.273</v>
+      </c>
+      <c r="T5" s="2" t="n">
         <v>441241</v>
       </c>
-      <c r="O5" t="n">
+      <c r="U5" s="2" t="n">
         <v>16196</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="V5" s="2" t="n">
+        <v>4072</v>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>5470</v>
-      </c>
-      <c r="R5" t="n">
-        <v>345</v>
-      </c>
-      <c r="S5" t="n">
-        <v>258</v>
       </c>
     </row>
     <row r="6">
@@ -829,7 +913,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T2 overhead only</t>
+          <t>T2 · close-range only</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -842,52 +926,64 @@
           <t>exp_091</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>95.17</v>
+      <c r="E6" t="n">
+        <v>91.45</v>
       </c>
       <c r="F6" t="n">
-        <v>93.87</v>
-      </c>
-      <c r="G6" t="n">
-        <v>96.34999999999999</v>
+        <v>96.04000000000001</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>93.69</v>
       </c>
       <c r="H6" t="n">
-        <v>90.81999999999999</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>99.95999999999999</v>
+        <v>99.88</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9370000000000001</v>
+        <v>99.92</v>
       </c>
       <c r="K6" t="n">
-        <v>0.617</v>
+        <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>1.188</v>
+        <v>100</v>
       </c>
       <c r="M6" t="n">
         <v>100</v>
       </c>
       <c r="N6" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="O6" t="n">
+        <v>92.37</v>
+      </c>
+      <c r="P6" t="n">
+        <v>94.95</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.209</v>
+      </c>
+      <c r="T6" t="n">
         <v>750396</v>
       </c>
-      <c r="O6" t="n">
+      <c r="U6" t="n">
         <v>12872</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="V6" t="n">
+        <v>2676</v>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>3495</v>
-      </c>
-      <c r="R6" t="n">
-        <v>331</v>
-      </c>
-      <c r="S6" t="n">
-        <v>258</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +994,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T3 full orbit only</t>
+          <t>T3 · distant only</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -912,120 +1008,144 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>95.01000000000001</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>93.72</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>96.23999999999999</v>
+        <v>93.66</v>
       </c>
       <c r="H7" t="n">
-        <v>90.48999999999999</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>100</v>
+        <v>99.72</v>
       </c>
       <c r="J7" t="n">
-        <v>1.164</v>
+        <v>99.86</v>
       </c>
       <c r="K7" t="n">
-        <v>0.874</v>
+        <v>100</v>
       </c>
       <c r="L7" t="n">
-        <v>1.367</v>
+        <v>100</v>
       </c>
       <c r="M7" t="n">
         <v>100</v>
       </c>
       <c r="N7" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="O7" t="n">
+        <v>92.31999999999999</v>
+      </c>
+      <c r="P7" t="n">
+        <v>94.83</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.189</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.381</v>
+      </c>
+      <c r="T7" t="n">
         <v>482225</v>
       </c>
-      <c r="O7" t="n">
+      <c r="U7" t="n">
         <v>13029</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="V7" t="n">
+        <v>2580</v>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>3516</v>
-      </c>
-      <c r="R7" t="n">
-        <v>333</v>
-      </c>
-      <c r="S7" t="n">
-        <v>258</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>information_sign_002</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>T1 close-ups+orbit</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>T1 · close-range + distant</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>COLMAP</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>exp_081</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>63.53</v>
-      </c>
-      <c r="F8" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="G8" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="H8" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="I8" t="n">
-        <v>69.22</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.223</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.694</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.545</v>
-      </c>
-      <c r="M8" t="n">
-        <v>100</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="E8" s="2" t="n">
+        <v>78.53</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>99.52</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>89.98</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>94.51000000000001</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>96.69</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>98.28</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>71.36</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>76.05</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>1.786</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>1.948</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>1.737</v>
+      </c>
+      <c r="T8" s="2" t="n">
         <v>547654</v>
       </c>
-      <c r="O8" t="n">
-        <v>8754</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>7/3/5</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>3865</v>
-      </c>
-      <c r="R8" t="n">
-        <v>796</v>
-      </c>
-      <c r="S8" t="n">
-        <v>598</v>
+      <c r="U8" s="2" t="n">
+        <v>25404</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>14198</v>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>5/2/3</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1036,7 +1156,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T2 overhead only</t>
+          <t>T2 · close-range only</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1050,51 +1170,63 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>33.24</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>30.32</v>
+        <v>29.66</v>
       </c>
       <c r="G9" t="n">
-        <v>35.99</v>
+        <v>40.84</v>
       </c>
       <c r="H9" t="n">
-        <v>38.99</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>28.98</v>
+        <v>43.72</v>
       </c>
       <c r="J9" t="n">
-        <v>4.218</v>
+        <v>60.5</v>
       </c>
       <c r="K9" t="n">
-        <v>6.453</v>
+        <v>99.64</v>
       </c>
       <c r="L9" t="n">
-        <v>1.861</v>
+        <v>69.17</v>
       </c>
       <c r="M9" t="n">
-        <v>95.8</v>
+        <v>81.66</v>
       </c>
       <c r="N9" t="n">
+        <v>40.81</v>
+      </c>
+      <c r="O9" t="n">
+        <v>37.15</v>
+      </c>
+      <c r="P9" t="n">
+        <v>44.48</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.366</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6.463</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.945</v>
+      </c>
+      <c r="T9" t="n">
         <v>801528</v>
       </c>
-      <c r="O9" t="n">
-        <v>7669</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>7/3/5</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>5004</v>
-      </c>
-      <c r="R9" t="n">
-        <v>518</v>
-      </c>
-      <c r="S9" t="n">
-        <v>598</v>
+      <c r="U9" t="n">
+        <v>19421</v>
+      </c>
+      <c r="V9" t="n">
+        <v>15582</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>5/2/3</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1105,7 +1237,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T3 full orbit only</t>
+          <t>T3 · distant only</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1118,121 +1250,145 @@
           <t>exp_083</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>71.33</v>
+      <c r="E10" t="n">
+        <v>73.59</v>
       </c>
       <c r="F10" t="n">
-        <v>68.91</v>
-      </c>
-      <c r="G10" t="n">
-        <v>73.72</v>
+        <v>79.41</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>76.39</v>
       </c>
       <c r="H10" t="n">
-        <v>63.1</v>
+        <v>99.56</v>
       </c>
       <c r="I10" t="n">
-        <v>82.03</v>
+        <v>88.61</v>
       </c>
       <c r="J10" t="n">
-        <v>1.972</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>1.193</v>
+        <v>99.83</v>
       </c>
       <c r="L10" t="n">
-        <v>1.589</v>
-      </c>
-      <c r="M10" t="n">
-        <v>100</v>
+        <v>97.33</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>98.56999999999999</v>
       </c>
       <c r="N10" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="O10" t="n">
+        <v>74.27</v>
+      </c>
+      <c r="P10" t="n">
+        <v>78.45999999999999</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.214</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.686</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="T10" t="n">
         <v>716317</v>
       </c>
-      <c r="O10" t="n">
-        <v>12643</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>7/3/5</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>5703</v>
-      </c>
-      <c r="R10" t="n">
-        <v>960</v>
-      </c>
-      <c r="S10" t="n">
-        <v>598</v>
+      <c r="U10" t="n">
+        <v>35676</v>
+      </c>
+      <c r="V10" t="n">
+        <v>21922</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>5/2/3</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>information_sign_002</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>T1 close-ups+orbit</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>T1 · close-range + distant</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>MASt3R-GA</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>exp_084</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>78.26000000000001</v>
-      </c>
-      <c r="F11" t="n">
-        <v>76.48999999999999</v>
-      </c>
-      <c r="G11" t="n">
-        <v>79.91</v>
-      </c>
-      <c r="H11" t="n">
-        <v>64.72</v>
-      </c>
-      <c r="I11" t="n">
-        <v>98.97</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2.199</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.744</v>
-      </c>
-      <c r="M11" t="n">
-        <v>100</v>
-      </c>
-      <c r="N11" t="n">
+        <v>75.52</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>99.05</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>99.86</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>99.93000000000001</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>84.45999999999999</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>86.92</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>1.859</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>1.725</v>
+      </c>
+      <c r="T11" s="2" t="n">
         <v>540530</v>
       </c>
-      <c r="O11" t="n">
-        <v>23591</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>7/3/5</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>9457</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1299</v>
-      </c>
-      <c r="S11" t="n">
-        <v>598</v>
+      <c r="U11" s="2" t="n">
+        <v>75146</v>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>36753</v>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>5/2/3</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1243,7 +1399,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T2 overhead only</t>
+          <t>T2 · close-range only</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1257,51 +1413,63 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>37.68</v>
+        <v>49.74</v>
       </c>
       <c r="F12" t="n">
-        <v>35.4</v>
+        <v>51.29</v>
       </c>
       <c r="G12" t="n">
-        <v>39.97</v>
+        <v>50.5</v>
       </c>
       <c r="H12" t="n">
-        <v>30.17</v>
+        <v>99.31</v>
       </c>
       <c r="I12" t="n">
-        <v>50.17</v>
+        <v>67.97</v>
       </c>
       <c r="J12" t="n">
-        <v>4.371</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>2.984</v>
+        <v>99.58</v>
       </c>
       <c r="L12" t="n">
-        <v>1.907</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N12" t="n">
+        <v>46.49</v>
+      </c>
+      <c r="O12" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="P12" t="n">
+        <v>53.08</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.014</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.841</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="T12" t="n">
         <v>1129311</v>
       </c>
-      <c r="O12" t="n">
-        <v>23749</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>7/3/5</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>12258</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1369</v>
-      </c>
-      <c r="S12" t="n">
-        <v>598</v>
+      <c r="U12" t="n">
+        <v>70386</v>
+      </c>
+      <c r="V12" t="n">
+        <v>49235</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>5/2/3</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1312,7 +1480,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>T3 full orbit only</t>
+          <t>T3 · distant only</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1326,388 +1494,62 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>78.04000000000001</v>
+        <v>80.11</v>
       </c>
       <c r="F13" t="n">
-        <v>75.98999999999999</v>
-      </c>
-      <c r="G13" t="n">
-        <v>80.09</v>
+        <v>96.65000000000001</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>87.61</v>
       </c>
       <c r="H13" t="n">
-        <v>65.7</v>
+        <v>99.87</v>
       </c>
       <c r="I13" t="n">
-        <v>96.09</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>2.01</v>
+        <v>99.83</v>
       </c>
       <c r="K13" t="n">
-        <v>0.923</v>
+        <v>99.94</v>
       </c>
       <c r="L13" t="n">
-        <v>1.647</v>
+        <v>100</v>
       </c>
       <c r="M13" t="n">
-        <v>100</v>
+        <v>99.97</v>
       </c>
       <c r="N13" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="O13" t="n">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="P13" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.649</v>
+      </c>
+      <c r="T13" t="n">
         <v>484330</v>
       </c>
-      <c r="O13" t="n">
-        <v>18121</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>7/3/5</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>7128</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1064</v>
-      </c>
-      <c r="S13" t="n">
-        <v>598</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>method</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>T1 F1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>T2 F1</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>T3 F1</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>spread (max-min)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>spread CI lo</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>spread CI hi</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>best approach</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>worst approach</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>best vs worst CIs overlap</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>bollard_003</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>COLMAP</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>80.17</v>
-      </c>
-      <c r="D2" t="n">
-        <v>84.56</v>
-      </c>
-      <c r="E2" t="n">
-        <v>84.04000000000001</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H2" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>yes (within noise)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>bollard_003</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MASt3R-GA</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>93.79000000000001</v>
-      </c>
-      <c r="D3" t="n">
-        <v>95.17</v>
-      </c>
-      <c r="E3" t="n">
-        <v>95.01000000000001</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>yes (within noise)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>information_sign_002</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>COLMAP</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>63.53</v>
-      </c>
-      <c r="D4" t="n">
-        <v>33.24</v>
-      </c>
-      <c r="E4" t="n">
-        <v>71.33</v>
-      </c>
-      <c r="F4" t="n">
-        <v>38.09</v>
-      </c>
-      <c r="G4" t="n">
-        <v>34.38</v>
-      </c>
-      <c r="H4" t="n">
-        <v>42</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>no (resolvable)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>information_sign_002</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>MASt3R-GA</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>78.26000000000001</v>
-      </c>
-      <c r="D5" t="n">
-        <v>37.68</v>
-      </c>
-      <c r="E5" t="n">
-        <v>78.04000000000001</v>
-      </c>
-      <c r="F5" t="n">
-        <v>40.58</v>
-      </c>
-      <c r="G5" t="n">
-        <v>38.19</v>
-      </c>
-      <c r="H5" t="n">
-        <v>43.79</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>no (resolvable)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>per-object mean spread:</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>bollard_003</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>mean spread</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>max</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>within noise</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>information_sign_002</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>mean spread</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>39.34</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>max</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>40.58</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>resolvable</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CI method: spatial block bootstrap, 2000 draws, 5.0 cm blocks</t>
+      <c r="U13" t="n">
+        <v>59039</v>
+      </c>
+      <c r="V13" t="n">
+        <v>28083</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>5/2/3</t>
         </is>
       </c>
     </row>

--- a/docs/tables/capture_comparison_summary.xlsx
+++ b/docs/tables/capture_comparison_summary.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="capture_comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="significance" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,6 +32,14 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00585D54"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000D8054"/>
     </font>
   </fonts>
   <fills count="3">
@@ -63,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -71,6 +80,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W13"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -458,10 +469,11 @@
     <col width="15" customWidth="1" min="17" max="17"/>
     <col width="17" customWidth="1" min="18" max="18"/>
     <col width="17" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -562,20 +574,25 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>reg-rate (%)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>points raw</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>points density-matched</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>excluded as gap</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>DBSCAN (ft/eps/mp)</t>
         </is>
@@ -648,15 +665,18 @@
         <v>1.301</v>
       </c>
       <c r="T2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U2" s="2" t="n">
         <v>105933</v>
       </c>
-      <c r="U2" s="2" t="n">
+      <c r="V2" s="2" t="n">
         <v>3847</v>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="W2" s="2" t="n">
         <v>754</v>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -729,15 +749,18 @@
         <v>1.11</v>
       </c>
       <c r="T3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U3" t="n">
         <v>36609</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>2715</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>419</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -810,15 +833,18 @@
         <v>1.418</v>
       </c>
       <c r="T4" t="n">
+        <v>100</v>
+      </c>
+      <c r="U4" t="n">
         <v>167287</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>5592</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>1295</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -891,15 +917,18 @@
         <v>1.273</v>
       </c>
       <c r="T5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U5" s="2" t="n">
         <v>441241</v>
       </c>
-      <c r="U5" s="2" t="n">
+      <c r="V5" s="2" t="n">
         <v>16196</v>
       </c>
-      <c r="V5" s="2" t="n">
+      <c r="W5" s="2" t="n">
         <v>4072</v>
       </c>
-      <c r="W5" s="2" t="inlineStr">
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -972,15 +1001,18 @@
         <v>1.209</v>
       </c>
       <c r="T6" t="n">
+        <v>100</v>
+      </c>
+      <c r="U6" t="n">
         <v>750396</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>12872</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>2676</v>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -1053,15 +1085,18 @@
         <v>1.381</v>
       </c>
       <c r="T7" t="n">
+        <v>100</v>
+      </c>
+      <c r="U7" t="n">
         <v>482225</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>13029</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>2580</v>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -1134,15 +1169,18 @@
         <v>1.737</v>
       </c>
       <c r="T8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U8" s="2" t="n">
         <v>547654</v>
       </c>
-      <c r="U8" s="2" t="n">
+      <c r="V8" s="2" t="n">
         <v>25404</v>
       </c>
-      <c r="V8" s="2" t="n">
+      <c r="W8" s="2" t="n">
         <v>14198</v>
       </c>
-      <c r="W8" s="2" t="inlineStr">
+      <c r="X8" s="2" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -1215,15 +1253,18 @@
         <v>1.945</v>
       </c>
       <c r="T9" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="U9" t="n">
         <v>801528</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>19421</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>15582</v>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -1296,15 +1337,18 @@
         <v>1.963</v>
       </c>
       <c r="T10" t="n">
+        <v>100</v>
+      </c>
+      <c r="U10" t="n">
         <v>716317</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>35676</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>21922</v>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -1377,15 +1421,18 @@
         <v>1.725</v>
       </c>
       <c r="T11" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U11" s="2" t="n">
         <v>540530</v>
       </c>
-      <c r="U11" s="2" t="n">
+      <c r="V11" s="2" t="n">
         <v>75146</v>
       </c>
-      <c r="V11" s="2" t="n">
+      <c r="W11" s="2" t="n">
         <v>36753</v>
       </c>
-      <c r="W11" s="2" t="inlineStr">
+      <c r="X11" s="2" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -1458,15 +1505,18 @@
         <v>1.912</v>
       </c>
       <c r="T12" t="n">
+        <v>100</v>
+      </c>
+      <c r="U12" t="n">
         <v>1129311</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>70386</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>49235</v>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>5/2/3</t>
         </is>
@@ -1539,17 +1589,459 @@
         <v>1.649</v>
       </c>
       <c r="T13" t="n">
+        <v>100</v>
+      </c>
+      <c r="U13" t="n">
         <v>484330</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>59039</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>28083</v>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>5/2/3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Pairwise F1@3cm differences, 2000 spatial block-bootstrap draws, 5.0 cm blocks. CI spanning 0 = not resolvable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>ΔF1@3cm (pp)</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>95% CI lo</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>95% CI hi</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>resolvable?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>T1−T2</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-8.17</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>T1−T3</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-8.74</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>T2−T3</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-4.84</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>T1−T2</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-2.58</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>T1−T3</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>T2−T3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>T1−T2</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>32.96</v>
+      </c>
+      <c r="E10" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="F10" t="n">
+        <v>37.23</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>T1−T3</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-5.73</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>COLMAP</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>T2−T3</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-35.55</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-39.73</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-31.26</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>T1−T2</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>32.45</v>
+      </c>
+      <c r="F13" t="n">
+        <v>38.23</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>T1−T3</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MASt3R-GA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>T2−T3</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-37.11</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-40.16</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-34.27</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>

--- a/docs/tables/capture_comparison_summary.xlsx
+++ b/docs/tables/capture_comparison_summary.xlsx
@@ -569,7 +569,7 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>inlier RMSE@3cm (cm)</t>
+          <t>inlier RMSE@3cm (mm)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
@@ -662,7 +662,7 @@
         <v>1.854</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>1.301</v>
+        <v>13.01</v>
       </c>
       <c r="T2" s="2" t="n">
         <v>100</v>
@@ -746,7 +746,7 @@
         <v>1.688</v>
       </c>
       <c r="S3" t="n">
-        <v>1.11</v>
+        <v>11.1</v>
       </c>
       <c r="T3" t="n">
         <v>100</v>
@@ -830,7 +830,7 @@
         <v>1.584</v>
       </c>
       <c r="S4" t="n">
-        <v>1.418</v>
+        <v>14.18</v>
       </c>
       <c r="T4" t="n">
         <v>100</v>
@@ -914,7 +914,7 @@
         <v>0.53</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>1.273</v>
+        <v>12.73</v>
       </c>
       <c r="T5" s="2" t="n">
         <v>100</v>
@@ -998,7 +998,7 @@
         <v>0.641</v>
       </c>
       <c r="S6" t="n">
-        <v>1.209</v>
+        <v>12.09</v>
       </c>
       <c r="T6" t="n">
         <v>100</v>
@@ -1082,7 +1082,7 @@
         <v>0.897</v>
       </c>
       <c r="S7" t="n">
-        <v>1.381</v>
+        <v>13.81</v>
       </c>
       <c r="T7" t="n">
         <v>100</v>
@@ -1166,7 +1166,7 @@
         <v>1.948</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>1.737</v>
+        <v>17.37</v>
       </c>
       <c r="T8" s="2" t="n">
         <v>100</v>
@@ -1250,7 +1250,7 @@
         <v>6.463</v>
       </c>
       <c r="S9" t="n">
-        <v>1.945</v>
+        <v>19.45</v>
       </c>
       <c r="T9" t="n">
         <v>95.8</v>
@@ -1334,7 +1334,7 @@
         <v>1.686</v>
       </c>
       <c r="S10" t="n">
-        <v>1.963</v>
+        <v>19.63</v>
       </c>
       <c r="T10" t="n">
         <v>100</v>
@@ -1418,7 +1418,7 @@
         <v>0.577</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>1.725</v>
+        <v>17.25</v>
       </c>
       <c r="T11" s="2" t="n">
         <v>100</v>
@@ -1502,7 +1502,7 @@
         <v>2.841</v>
       </c>
       <c r="S12" t="n">
-        <v>1.912</v>
+        <v>19.12</v>
       </c>
       <c r="T12" t="n">
         <v>100</v>
@@ -1586,7 +1586,7 @@
         <v>0.716</v>
       </c>
       <c r="S13" t="n">
-        <v>1.649</v>
+        <v>16.49</v>
       </c>
       <c r="T13" t="n">
         <v>100</v>
